--- a/ExportOrderWebServer/Resources/CargoManifest.xlsx
+++ b/ExportOrderWebServer/Resources/CargoManifest.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Dropbox\Axion+\Soling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\source\repos\AxionPlus\ExportOrderWebServer\ExportOrderWebServer\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF11C52-5655-4DEC-BB0B-B73F64E5F14B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C972DD5E-C41E-4C0B-B5AE-C91C9963418A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="25580" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CM" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">CM!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>VESSEL NAME:</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>AGRICULTURAL &amp; INDUSTRIAL TYRES</t>
-  </si>
-  <si>
-    <t>3840</t>
   </si>
   <si>
     <t>2512N</t>
@@ -373,7 +370,7 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -442,11 +439,17 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="17" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="17" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -952,13 +955,13 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L1" s="11">
         <v>45782</v>
@@ -971,7 +974,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -979,50 +982,50 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>20</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>21</v>
       </c>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
     </row>
-    <row r="3" spans="1:13" s="25" customFormat="1" ht="40" customHeight="1">
+    <row r="3" spans="1:13" s="24" customFormat="1" ht="40" customHeight="1">
       <c r="A3" s="20"/>
       <c r="B3" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="24"/>
+      <c r="H3" s="25"/>
       <c r="I3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>27</v>
-      </c>
       <c r="K3" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="14.5">
@@ -1041,16 +1044,16 @@
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
+      <c r="F4" s="27">
+        <v>3840</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="26" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -1063,7 +1066,7 @@
         <v>29334.799999999999</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
